--- a/artfynd/A 34459-2022 artfynd.xlsx
+++ b/artfynd/A 34459-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 34459-2022 artfynd.xlsx
+++ b/artfynd/A 34459-2022 artfynd.xlsx
@@ -1473,7 +1473,7 @@
         <v>119738227</v>
       </c>
       <c r="B8" t="n">
-        <v>100080</v>
+        <v>100103</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 34459-2022 artfynd.xlsx
+++ b/artfynd/A 34459-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1580,6 +1580,107 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>130818800</v>
+      </c>
+      <c r="B9" t="n">
+        <v>75216</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>101</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Matt pricklav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Pachnolepia pruinata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Pers.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Dalkarskärret väst P-plats, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>645187</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6629325</v>
+      </c>
+      <c r="S9" t="n">
+        <v>26</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Uppsala-Näs</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Kenth Kärsrud</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Kenth Kärsrud</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34459-2022 artfynd.xlsx
+++ b/artfynd/A 34459-2022 artfynd.xlsx
@@ -1585,7 +1585,7 @@
         <v>130818800</v>
       </c>
       <c r="B9" t="n">
-        <v>75216</v>
+        <v>75217</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 34459-2022 artfynd.xlsx
+++ b/artfynd/A 34459-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,74 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>64621234</v>
+        <v>130818800</v>
       </c>
       <c r="B2" t="n">
-        <v>57575</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75318</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208250</v>
+        <v>101</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Matt pricklav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Pachnolepia pruinata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Pers.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Dalkarlskärret, Upl</t>
+          <t>Dalkarskärret väst P-plats, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>645022.206365061</v>
+        <v>645187</v>
       </c>
       <c r="R2" t="n">
-        <v>6629170.196691145</v>
+        <v>6629325</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -761,114 +738,86 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Dalby</t>
+          <t>Uppsala-Näs</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-03-27</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>13:05</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-03-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>13:05</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Niklas Hjort</t>
+          <t>Kenth Kärsrud</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Niklas Hjort</t>
+          <t>Kenth Kärsrud</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>100676486</v>
+        <v>56710953</v>
       </c>
       <c r="B3" t="n">
-        <v>57150</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91502</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208260</v>
+        <v>3086</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Auricularia mesenterica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Dicks.:Fr.) Pers.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hammarskogs friluftsområde, Upl</t>
+          <t>Dalkarlskärret, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>644578.5660905743</v>
+        <v>645134</v>
       </c>
       <c r="R3" t="n">
-        <v>6628787.434548391</v>
+        <v>6629280</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -887,32 +836,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Dalby</t>
+          <t>Uppsala-Näs</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2015-07-29</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-01-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2015-07-29</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-01-26</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1 ex.</t>
+          <t>stor upplagd lövrishög</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,36 +862,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Skogsbryn vid åker och väg.</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Owe Rosengren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Owe Rosengren, Patrick Fritzson, Tor Jonzon</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>101017746</v>
+        <v>81131989</v>
       </c>
       <c r="B4" t="n">
-        <v>57140</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92333</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -960,40 +889,40 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100088</v>
+        <v>4217</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Uppsala, Upl</t>
+          <t>Dalkarlskärret, parkering, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>644735.8022053367</v>
+        <v>645162</v>
       </c>
       <c r="R4" t="n">
-        <v>6629094.517629383</v>
+        <v>6629331</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1012,27 +941,17 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Dalby</t>
+          <t>Uppsala-Näs</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-05-21</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>16:04</t>
+          <t>2019-12-09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-05-21</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>16:04</t>
+          <t>2019-12-09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,33 +960,44 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>vanlig tall</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris var. sylvestris</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris var. sylvestris</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Björn Bråvander</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ward Tamsyn, Margaux Boeraeve</t>
+          <t>Björn Bråvander, Patrick Fritzson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>108311102</v>
+        <v>103803690</v>
       </c>
       <c r="B5" t="n">
-        <v>57549</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,66 +1005,47 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>208245</v>
+        <v>4769</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>i vatten/simmande</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bäck Ö Dalkarlskärret, Upl</t>
+          <t>Svälthammar, Hammarskogs NR, Uppsala, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>645169.0688295362</v>
+        <v>644724</v>
       </c>
       <c r="R5" t="n">
-        <v>6629288.843523184</v>
+        <v>6629012</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1153,32 +1064,17 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Uppsala-Näs</t>
+          <t>Dalby</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-04-20</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>20:00</t>
+          <t>2022-09-27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-04-20</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>20:30</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>I bäcken Ö Dalkarlskärret, de flesta i den djupare delen som formats när kommunen nyligen byggt cykelbana.</t>
+          <t>2022-09-27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1187,97 +1083,75 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Göran Sahlén</t>
+          <t>Johan Lindell</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Göran Sahlén</t>
+          <t>Johan Lindell</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>108358392</v>
+        <v>56038192</v>
       </c>
       <c r="B6" t="n">
-        <v>57575</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>208250</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>äggklumpar</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>ägg</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>i vatten/simmande</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bäck Ö Dalkarlskärret, Upl</t>
+          <t>Hammarskogs friluftsområde, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>645169.0688295362</v>
+        <v>644702</v>
       </c>
       <c r="R6" t="n">
-        <v>6629288.843523184</v>
+        <v>6628963</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1296,27 +1170,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Uppsala-Näs</t>
+          <t>Dalby</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-04-22</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-07-23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-04-22</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-07-23</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>1 ex. på död, kvarsittande gren 11 m upp + 3 ex. i gamla grensår 3, 4 och 10 m upp på stammen av levande tall, omkr. 150 cm.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1325,86 +1194,91 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Barr-/blandskog.</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Död, kvarsittande gren och gamla grensår på stammen av levande tall. # Tall</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Göran Sahlén</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Göran Sahlén</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>109560467</v>
+        <v>96920666</v>
       </c>
       <c r="B7" t="n">
-        <v>6600</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100763</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cinnoberbagge</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cucujus cinnaberinus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>frispringande/krypande</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ytternäs, Upl</t>
+          <t>Hammarskog, Uppsala, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>645661.2450984034</v>
+        <v>644700</v>
       </c>
       <c r="R7" t="n">
-        <v>6629602.463827783</v>
+        <v>6628973</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1423,27 +1297,17 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Uppsala-Näs</t>
+          <t>Dalby</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-05-27</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-05-27</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1454,31 +1318,41 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Mats Jonsell</t>
+          <t>Johan Lindell</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Mats Jonsell</t>
+          <t>Johan Lindell</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119738227</v>
+        <v>103666556</v>
       </c>
       <c r="B8" t="n">
-        <v>100103</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92928</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1486,34 +1360,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222771</v>
+        <v>5836</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Guldkremla</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Russula aurea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Pers.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Dalkarlskärret, Dalkarlskärret, Upl</t>
+          <t>Hammarskog: Dalkarlskärret, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>645186</v>
+        <v>645101</v>
       </c>
       <c r="R8" t="n">
-        <v>6629325</v>
+        <v>6629263</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1535,27 +1412,17 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Uppsala-Näs</t>
+          <t>Dalby</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>11:44</t>
+          <t>2022-09-19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>11:44</t>
+          <t>2022-09-19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1564,69 +1431,86 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>tall, gran, ek, björk</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Moa Christoffersson</t>
+          <t>Björn Larsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Moa Christoffersson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Monica Andersson, Åsa Kruys, Annica Beil, Mattias Sonemar, Katrin Björk, Johanna Hellberg, Suzanne Kolare</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>SMF:s mykologivecka</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130818800</v>
+        <v>103803594</v>
       </c>
       <c r="B9" t="n">
-        <v>75240</v>
+        <v>92928</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>101</v>
+        <v>5836</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Matt pricklav</t>
+          <t>Guldkremla</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pachnolepia pruinata</t>
+          <t>Russula aurea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Pers.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>Pers.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Dalkarskärret väst P-plats, Upl</t>
+          <t>Svälthammar, Hammarskogs NR, Uppsala, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>645187</v>
+        <v>644723</v>
       </c>
       <c r="R9" t="n">
-        <v>6629325</v>
+        <v>6629044</v>
       </c>
       <c r="S9" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1645,48 +1529,47 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Uppsala-Näs</t>
+          <t>Dalby</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2022-09-27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2022-09-27</t>
         </is>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF9" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kenth Kärsrud</t>
+          <t>Johan Lindell</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kenth Kärsrud</t>
+          <t>Johan Lindell</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131538272</v>
+        <v>56001805</v>
       </c>
       <c r="B10" t="n">
-        <v>57908</v>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1694,38 +1577,41 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102977</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Dalkarlskärret, Upl</t>
+          <t>Hammarskogs friluftsområde, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>644708</v>
+        <v>644680</v>
       </c>
       <c r="R10" t="n">
-        <v>6629031</v>
+        <v>6628873</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1752,22 +1638,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>11:44</t>
+          <t>1998-05-24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>11:44</t>
+          <t>1998-05-24</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2 äldre bohål i levande tall, omkr. 137 cm.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1782,15 +1663,4166 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>101017746</v>
+      </c>
+      <c r="B11" t="n">
+        <v>56895</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100088</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vanlig snok</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Natrix natrix</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Uppsala, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>644736</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6629095</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2022-05-21</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2022-05-21</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn, Margaux Boeraeve</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>77451269</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57194</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100114</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Gråhakedopping</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Podiceps grisegena</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Boddaert, 1783)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Uppsala, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>645170</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6629327</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Uppsala-Näs</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2019-05-01</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2019-05-01</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Jessica Ingman</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Jessica Ingman, Gunnar Lundström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>108352820</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58829</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100141</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Större vattensalamander</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Triturus cristatus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Laurenti, 1768)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>trafikdödad</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Vägen Dalkarlskärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>645201</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6629410</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Uppsala-Näs</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-04-21</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-04-21</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>78525896</v>
+      </c>
+      <c r="B14" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Svälthammer, Hammarskog NR, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>644730</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6629112</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2019-06-21</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2019-06-21</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Niklas Hjort</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Niklas Hjort</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>78597459</v>
+      </c>
+      <c r="B15" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Svälthammar, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>644714</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6629106</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2019-06-23</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2019-06-23</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Karin Wiklund</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Karin Wiklund</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>109560467</v>
+      </c>
+      <c r="B16" t="n">
+        <v>6675</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100763</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Cinnoberbagge</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Cucujus cinnaberinus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ytternäs, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>645662</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6629603</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Uppsala-Näs</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2023-05-27</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2023-05-27</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Mats Jonsell</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Mats Jonsell</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>77248144</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58129</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>102623</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Trädlärka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lullula arborea</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Svälthammar, Dalkarlskärret, Uppsala-Näs, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>644728</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6629100</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2019-04-22</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2019-04-22</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Gunnar Siljestrand</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Gunnar Siljestrand, Birgitta Davidsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>77737459</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57364</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>102954</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Enkelbeckasin</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Gallinago gallinago</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Uppsala, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>645170</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6629314</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Uppsala-Näs</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2019-05-13</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>19:39</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2019-05-13</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>19:39</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Arne Wallin</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Arne Wallin</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>67960651</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57947</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Dalkarlskärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>645167</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6629328</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Uppsala-Näs</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2017-10-15</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2017-10-15</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
           <t>David van der Spoel</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="AX19" t="inlineStr">
         <is>
           <t>David van der Spoel</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr"/>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>131538272</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57947</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Dalkarlskärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>644708</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6629031</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>David van der Spoel</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>David van der Spoel</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>77393406</v>
+      </c>
+      <c r="B21" t="n">
+        <v>58238</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Dalkarlskärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>645157</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6629303</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Uppsala-Näs</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2019-04-29</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2019-04-29</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>David van der Spoel</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>David van der Spoel</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>77451274</v>
+      </c>
+      <c r="B22" t="n">
+        <v>58238</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Uppsala, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>645170</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6629327</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Uppsala-Näs</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2019-05-01</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2019-05-01</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Jessica Ingman</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Jessica Ingman, Gunnar Lundström</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>86303473</v>
+      </c>
+      <c r="B23" t="n">
+        <v>58238</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Svälthammar, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>644729</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6629099</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2020-06-16</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2020-06-16</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Håkan Lernefalk</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Håkan Lernefalk</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>77393410</v>
+      </c>
+      <c r="B24" t="n">
+        <v>58439</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Dalkarlskärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>645159</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6629290</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Uppsala-Näs</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2019-04-29</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2019-04-29</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>David van der Spoel</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>David van der Spoel</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>125163270</v>
+      </c>
+      <c r="B25" t="n">
+        <v>58439</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Dalkarlskärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>645157</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6629337</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Uppsala-Näs</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>David van der Spoel</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>David van der Spoel</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>77737461</v>
+      </c>
+      <c r="B26" t="n">
+        <v>58353</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>103037</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Stare</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Sturnus vulgaris</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Uppsala, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>645170</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6629314</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Uppsala-Näs</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2019-05-13</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>19:57</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2019-05-13</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>19:57</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Arne Wallin</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Arne Wallin</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>77135120</v>
+      </c>
+      <c r="B27" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Svälthammar, 300 m SV Dalkarlskärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>644728</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6629111</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2019-04-19</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2019-04-19</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På timmerupplag</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Rasmus Elleby</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Rasmus Elleby</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>77182030</v>
+      </c>
+      <c r="B28" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Svälthammer, Hammarskogs NR, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>644731</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6629111</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2019-04-20</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2019-04-20</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På timmertrave med främst gran.</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Owe Rosengren</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Owe Rosengren, Åke Berg, Kenth Kärsrud</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>77225098</v>
+      </c>
+      <c r="B29" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Svälthammar, Dalkarlskärret, Uppsala-Näs, Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>644728</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6629100</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2019-04-22</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2019-04-22</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Timmerupplag.</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Gunnar Siljestrand</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Gunnar Siljestrand, Birgitta Davidsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>77225903</v>
+      </c>
+      <c r="B30" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Svälthammer, Hammarskog NR, Upl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>644730</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6629112</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2019-04-22</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2019-04-22</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Niklas Hjort</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Niklas Hjort, Owe Rosengren, Åke Berg, Håkan Lernefalk</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>100275913</v>
+      </c>
+      <c r="B31" t="n">
+        <v>58085</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Dalkarlskärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>645169</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6629313</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Uppsala-Näs</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2022-04-27</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2022-04-27</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>David van der Spoel</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>David van der Spoel</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>93309995</v>
+      </c>
+      <c r="B32" t="n">
+        <v>56835</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Dalkarlskärret, parkeringen, Upl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>645159</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6629322</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Uppsala-Näs</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2021-05-08</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2021-05-08</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Jagade oblygt över parkeringen på ca 3-5 m höjd. Mycket liten med ljusbrun kroppspäls. Hungrig efter kyla och regn?</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Skogsbryn</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Sebastian Sundberg</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Sebastian Sundberg, Isak Sundberg Hjelm</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>70705551</v>
+      </c>
+      <c r="B33" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Dalkarlskärret, Hammarskog NR, Upl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>645161</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6629332</v>
+      </c>
+      <c r="S33" t="n">
+        <v>25</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Uppsala-Näs</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2018-04-17</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2018-04-17</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Niklas Hjort</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Niklas Hjort, Owe Rosengren, Tor Jonzon</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>65360311</v>
+      </c>
+      <c r="B34" t="n">
+        <v>58790</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Dalkarlskärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>645337</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6629495</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Uppsala-Näs</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2017-05-05</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2017-05-05</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Gammal individ som gick på vägen.</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Niklas Hjort</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Niklas Hjort</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>77139955</v>
+      </c>
+      <c r="B35" t="n">
+        <v>58790</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>parning/parningsceremonier</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Dalkarlskärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>645139</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6629288</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Uppsala-Näs</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2019-04-19</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2019-04-19</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Rasmus Elleby</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Rasmus Elleby</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>100204926</v>
+      </c>
+      <c r="B36" t="n">
+        <v>58790</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>parning/parningsceremonier</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Dalkarlskärret (ditch), Upl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>645137</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6629285</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Uppsala-Näs</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2022-04-23</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2022-04-23</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Loïs Rancilhac</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Loïs Rancilhac</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>108311102</v>
+      </c>
+      <c r="B37" t="n">
+        <v>58790</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Bäck Ö Dalkarlskärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>645169</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6629288</v>
+      </c>
+      <c r="S37" t="n">
+        <v>50</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Uppsala-Näs</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2023-04-20</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2023-04-20</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>I bäcken Ö Dalkarlskärret, de flesta i den djupare delen som formats när kommunen nyligen byggt cykelbana.</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Göran Sahlén</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Göran Sahlén</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>108352464</v>
+      </c>
+      <c r="B38" t="n">
+        <v>58790</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>trafikdödad</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Vägen Dalkarlskärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>644978</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6629156</v>
+      </c>
+      <c r="S38" t="n">
+        <v>25</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2023-04-21</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2023-04-21</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>64621234</v>
+      </c>
+      <c r="B39" t="n">
+        <v>58815</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Dalkarlskärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>645022</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6629170</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2017-03-27</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2017-03-27</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Niklas Hjort</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Niklas Hjort</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>72319320</v>
+      </c>
+      <c r="B40" t="n">
+        <v>58815</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Dalkarlskärret, Utloppet, Dalkarlskärret, Uppsala-Näs, Upl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>645176</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6629325</v>
+      </c>
+      <c r="S40" t="n">
+        <v>50</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Uppsala-Näs</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2018-07-18</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2018-07-18</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Fredrik Alriksson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Via Fredrik Alriksson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>108358392</v>
+      </c>
+      <c r="B41" t="n">
+        <v>58815</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>äggklumpar</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>ägg</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Bäck Ö Dalkarlskärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>645169</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6629288</v>
+      </c>
+      <c r="S41" t="n">
+        <v>50</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Uppsala-Näs</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2023-04-22</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2023-04-22</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Göran Sahlén</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Göran Sahlén</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>100676486</v>
+      </c>
+      <c r="B42" t="n">
+        <v>56905</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>208260</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Huggorm</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Vipera berus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Hammarskogs friluftsområde, Upl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>644579</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6628787</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2015-07-29</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2015-07-29</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>1 ex.</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Skogsbryn vid åker och väg.</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>79448568</v>
+      </c>
+      <c r="B43" t="n">
+        <v>108194</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220103</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Klasefibbla</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Crepis praemorsa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) Walther</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Hammarskogs NR, vid Dalkarlskärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>645141</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6629295</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Uppsala-Näs</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2019-06-11</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2019-06-11</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ca. 20 blommande plantor, vid vägkant intill ett dike.</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>Väg-/dikeskant.</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>115958183</v>
+      </c>
+      <c r="B44" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Dalkarlskärret, Dalkarlskärret, Uppsala-Näs, Upl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>645169</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6629347</v>
+      </c>
+      <c r="S44" t="n">
+        <v>25</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Uppsala-Näs</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-04-14</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-04-14</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Barbara Leibiger</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Barbara Leibiger, Ingo Leibiger</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>119738227</v>
+      </c>
+      <c r="B45" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Dalkarlskärret, Dalkarlskärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>645186</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6629325</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Uppsala-Näs</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Moa Christoffersson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Moa Christoffersson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
